--- a/data/trans_camb/IP16B05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Habitat-trans_camb.xlsx
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,4</t>
+          <t>0,0; 57,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,73</t>
+          <t>0,0; 50,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 0,0</t>
+          <t>-43,22; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 25,49</t>
+          <t>-10,38; 25,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,4</t>
+          <t>0,0; 31,02</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 101,61</t>
+          <t>0,0; 137,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 102,98</t>
+          <t>0,0; 102,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 0,0</t>
+          <t>-43,22; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 36,61</t>
+          <t>-10,43; 36,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,77</t>
+          <t>0,0; 44,98</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 24,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,44</t>
+          <t>0,0; 28,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,95</t>
+          <t>-2,25; 10,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,17</t>
+          <t>0,0; 31,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 40,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 11,04</t>
+          <t>-2,25; 11,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,34</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Habitat-trans_camb.xlsx
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,03</t>
+          <t>0,0; 50,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,6</t>
+          <t>0,0; 50,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 0,0</t>
+          <t>-46,62; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 25,29</t>
+          <t>-11,05; 25,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,02</t>
+          <t>0,0; 44,45</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 137,03</t>
+          <t>0,0; 102,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 102,44</t>
+          <t>0,0; 101,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 0,0</t>
+          <t>-46,62; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 36,4</t>
+          <t>-11,32; 35,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,98</t>
+          <t>0,0; 80,6</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,09</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,67</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,6</t>
+          <t>-2,93; 9,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,81</t>
+          <t>0,0; 13,66</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,74</t>
+          <t>0,0; 34,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,29</t>
+          <t>0,0; 43,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 11,94</t>
+          <t>-2,93; 10,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
     </row>
